--- a/xls/square_20_tri3_24.xlsx
+++ b/xls/square_20_tri3_24.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22">
+        <v>625</v>
+      </c>
+      <c r="C22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22">
+        <v>441</v>
+      </c>
+      <c r="E22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22">
+        <v>529</v>
+      </c>
+      <c r="G22" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22">
+        <v>2904</v>
+      </c>
+      <c r="I22">
+        <v>1.847279754245358</v>
+      </c>
+      <c r="J22">
+        <v>-1.3952238713627418</v>
+      </c>
+      <c r="K22">
+        <v>2.7512103521096303</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23">
+        <v>625</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23">
+        <v>441</v>
+      </c>
+      <c r="E23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23">
+        <v>576</v>
+      </c>
+      <c r="G23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23">
+        <v>3174</v>
+      </c>
+      <c r="I23">
+        <v>0.005666742077276533</v>
+      </c>
+      <c r="J23">
+        <v>-2.2501094435224713</v>
+      </c>
+      <c r="K23">
+        <v>2.0666531042568637</v>
+      </c>
+    </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
         <v>11</v>
